--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744678</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744678</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744678</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744678</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester, Helene Andersson</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744678</v>
+        <v>131734688</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gulåsen NV, Jmt</t>
+          <t>Djuphålet Sydost, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494672</v>
+        <v>494711</v>
       </c>
       <c r="R2" t="n">
-        <v>7124787</v>
+        <v>7124574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -736,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131736072</v>
+        <v>131738064</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,30 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupvattenedet Nordväst, Jmt</t>
+          <t>Djupvattenedet Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494931</v>
+        <v>495270</v>
       </c>
       <c r="R3" t="n">
-        <v>7124413</v>
+        <v>7124346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +880,7 @@
         <v>131739855</v>
       </c>
       <c r="B4" t="n">
-        <v>57948</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,208 +979,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131734688</v>
-      </c>
-      <c r="B5" t="n">
-        <v>79074</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Djuphålet Sydost, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>494711</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7124574</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131738064</v>
-      </c>
-      <c r="B6" t="n">
-        <v>80422</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Djupvattenedet Sydväst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>495270</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7124346</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 59523-2023 artfynd.xlsx
+++ b/artfynd/A 59523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>